--- a/data/safety_incidents.xlsx
+++ b/data/safety_incidents.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -59,6 +59,33 @@
   </si>
   <si>
     <t>Updated_At</t>
+  </si>
+  <si>
+    <t>6a2c560ed9d94550b004829978a7f0e3</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>08:33</t>
+  </si>
+  <si>
+    <t>Injury</t>
+  </si>
+  <si>
+    <t>Main Estate DG03000</t>
+  </si>
+  <si>
+    <t>Mr. Chigoga a tasker working under CCHL cut his little finger with a cane knife as he was trying to extinguish the malicious fire in DG03000.</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>6a2c560ed9d94550b004829978a7f0e3_903fb1398f824b6c8c5c5bc04876622c_INCIDENT_DG39-2.jpg</t>
+  </si>
+  <si>
+    <t>2025-12-03T06:35:25.683723</t>
   </si>
 </sst>
 </file>
@@ -416,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -466,6 +493,38 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
